--- a/ecv/ecv_unificada/panel_ecv_uraba.xlsx
+++ b/ecv/ecv_unificada/panel_ecv_uraba.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jimen\Documents\ecv_unificada\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jimen\Documents\encuesta_calidad_vida_antioquia\ecv_unificada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_1572FCDF8F79A8D366075C52F37BD2729ACD3E78" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF78C1C2-1A91-4706-8855-531EC91C5AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="46">
   <si>
     <t>dane_code</t>
   </si>
@@ -49,6 +49,9 @@
     <t>tasa_desempleo_total</t>
   </si>
   <si>
+    <t>dep_economica_total</t>
+  </si>
+  <si>
     <t>IMCV_urbano</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t>tasa_desempleo_urbano</t>
   </si>
   <si>
+    <t>dep_economica_urbano</t>
+  </si>
+  <si>
     <t>IMCV_rural</t>
   </si>
   <si>
@@ -83,6 +89,9 @@
   </si>
   <si>
     <t>tasa_desempleo_rural</t>
+  </si>
+  <si>
+    <t>dep_economica_rural</t>
   </si>
   <si>
     <t>05045</t>
@@ -501,10 +510,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U45"/>
+  <dimension ref="A1:X45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="24" max="24" width="21.21875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -568,13 +580,22 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C2">
         <v>2017</v>
@@ -598,24 +619,33 @@
         <v>15.1930050081607</v>
       </c>
       <c r="J2">
+        <v>49.591280653950903</v>
+      </c>
+      <c r="K2">
         <v>32.3679614775725</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>15.874794097085299</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
+        <v>47.425149700598801</v>
+      </c>
+      <c r="R2">
         <v>24.770033802816901</v>
       </c>
-      <c r="U2">
+      <c r="W2">
         <v>8.3728888237583305</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X2">
+        <v>56.390977443609003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>2019</v>
@@ -639,48 +669,57 @@
         <v>13.512626444889801</v>
       </c>
       <c r="J3">
+        <v>60.147317226593501</v>
+      </c>
+      <c r="K3">
         <v>32.859885603112801</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.46047340425531902</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>0.68617411347517698</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>1.7249854609929101</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>1.4759588652482301</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>13.9832226586282</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
+        <v>60.041023091027697</v>
+      </c>
+      <c r="R3">
         <v>28.541635869565201</v>
       </c>
-      <c r="Q3">
+      <c r="S3">
         <v>3.2987434554973799E-2</v>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>0.17495654450261799</v>
       </c>
-      <c r="S3">
+      <c r="U3">
         <v>0.43029895287958098</v>
       </c>
-      <c r="T3">
+      <c r="V3">
         <v>1.4994570680628301</v>
       </c>
-      <c r="U3">
+      <c r="W3">
         <v>10.159875098780301</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X3">
+        <v>60.845153883976103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>2021</v>
@@ -704,48 +743,54 @@
         <v>11.9655919329255</v>
       </c>
       <c r="J4">
+        <v>47.116657238808898</v>
+      </c>
+      <c r="K4">
         <v>33.938315476190503</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>0.662072169811321</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>0.87022264150943396</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>1.5724429245283</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>1.47360849056604</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>12.4433466086096</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
+        <v>46.317150424191603</v>
+      </c>
+      <c r="R4">
         <v>27.770525806451602</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>0</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>0.22518055555555599</v>
       </c>
-      <c r="S4">
+      <c r="U4">
         <v>1.37886944444444</v>
       </c>
-      <c r="T4">
+      <c r="V4">
         <v>1.48377222222222</v>
       </c>
-      <c r="U4">
+      <c r="W4">
         <v>8.8227691035053208</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>2023</v>
@@ -769,45 +814,51 @@
         <v>8.0523179181608295</v>
       </c>
       <c r="J5">
+        <v>45.799629243360101</v>
+      </c>
+      <c r="K5">
         <v>30.8545153846154</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>0.37844499999999998</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>0.56903375</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>1.6071662499999999</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>1.4727837500000001</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>8.2310719254670595</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
+        <v>44.655250686689797</v>
+      </c>
+      <c r="R5">
         <v>29.6414093333333</v>
       </c>
-      <c r="Q5">
+      <c r="S5">
         <v>7.3984536082474198E-2</v>
       </c>
-      <c r="S5">
+      <c r="U5">
         <v>0.97811958762886597</v>
       </c>
-      <c r="T5">
+      <c r="V5">
         <v>1.5031000000000001</v>
       </c>
-      <c r="U5">
+      <c r="W5">
         <v>6.65772671571826</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>2017</v>
@@ -831,24 +882,33 @@
         <v>22.400583371355701</v>
       </c>
       <c r="J6">
+        <v>59.811985898942403</v>
+      </c>
+      <c r="K6">
         <v>28.647073333333498</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>31.352420619716099</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
+        <v>61.575562700964603</v>
+      </c>
+      <c r="R6">
         <v>24.135012318840499</v>
       </c>
-      <c r="U6">
+      <c r="W6">
         <v>12.8454758533176</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X6">
+        <v>55.021834061135301</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>2019</v>
@@ -872,48 +932,57 @@
         <v>10.950486996252</v>
       </c>
       <c r="J7">
+        <v>62.708790261117798</v>
+      </c>
+      <c r="K7">
         <v>30.680264055299499</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>0.36531310043668103</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>0.54227947598253301</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>1.51400655021834</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>1.49398471615721</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>17.418231522686799</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
+        <v>62.855985980936097</v>
+      </c>
+      <c r="R7">
         <v>25.402198333333299</v>
       </c>
-      <c r="Q7">
+      <c r="S7">
         <v>0</v>
       </c>
-      <c r="R7">
+      <c r="T7">
         <v>3.3741935483871E-2</v>
       </c>
-      <c r="S7">
+      <c r="U7">
         <v>0.29509999999999997</v>
       </c>
-      <c r="T7">
+      <c r="V7">
         <v>1.4918774193548401</v>
       </c>
-      <c r="U7">
+      <c r="W7">
         <v>5.6328816157989596</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X7">
+        <v>62.601094744610897</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8">
         <v>2021</v>
@@ -937,45 +1006,51 @@
         <v>13.4793580211429</v>
       </c>
       <c r="J8">
+        <v>64.672708844990098</v>
+      </c>
+      <c r="K8">
         <v>30.208631666666701</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>0.187912631578947</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>0.36147157894736798</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>1.4412010526315799</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>1.4957757894736801</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>19.060144593139501</v>
       </c>
-      <c r="P8">
+      <c r="R8">
         <v>26.6726365853659</v>
       </c>
-      <c r="Q8">
+      <c r="S8">
         <v>2.80026666666667E-2</v>
       </c>
-      <c r="S8">
+      <c r="U8">
         <v>0.295902</v>
       </c>
-      <c r="T8">
+      <c r="V8">
         <v>1.475268</v>
       </c>
-      <c r="U8">
+      <c r="W8">
         <v>9.1004412929506309</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X8">
+        <v>70.9442978229728</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C9">
         <v>2023</v>
@@ -996,39 +1071,45 @@
         <v>11.3569438266688</v>
       </c>
       <c r="J9">
+        <v>62.903170814865298</v>
+      </c>
+      <c r="K9">
         <v>24.8124649635037</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>4.3452413793103502E-2</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>0.99880620689655197</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>1.4935027586206899</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>15.1790927468417</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
+        <v>52.742368332774298</v>
+      </c>
+      <c r="R9">
         <v>23.5077787234043</v>
       </c>
-      <c r="Q9">
+      <c r="S9">
         <v>3.6845614035087702E-2</v>
       </c>
-      <c r="T9">
+      <c r="V9">
         <v>1.5031000000000001</v>
       </c>
-      <c r="U9">
+      <c r="W9">
         <v>8.3948335273305101</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10">
         <v>2017</v>
@@ -1052,24 +1133,33 @@
         <v>6.0296869511016</v>
       </c>
       <c r="J10">
+        <v>41.051567239635901</v>
+      </c>
+      <c r="K10">
         <v>32.827614010988697</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>5.7533252081953501</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
+        <v>38.0758807588075</v>
+      </c>
+      <c r="R10">
         <v>26.255835416666599</v>
       </c>
-      <c r="U10">
+      <c r="W10">
         <v>6.8973711445279102</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X10">
+        <v>49.800796812748999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C11">
         <v>2019</v>
@@ -1093,48 +1183,57 @@
         <v>5.74565601614934</v>
       </c>
       <c r="J11">
+        <v>59.708936638231997</v>
+      </c>
+      <c r="K11">
         <v>28.557519696969699</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>0.32432937062937101</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>0.56010209790209797</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>1.60898811188811</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>1.4739055944055901</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>5.0413744449189997</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
+        <v>59.877367488758701</v>
+      </c>
+      <c r="R11">
         <v>26.9010573099415</v>
       </c>
-      <c r="Q11">
+      <c r="S11">
         <v>9.4839664804469301E-2</v>
       </c>
-      <c r="R11">
+      <c r="T11">
         <v>0.251915642458101</v>
       </c>
-      <c r="S11">
+      <c r="U11">
         <v>0.81437262569832403</v>
       </c>
-      <c r="T11">
+      <c r="V11">
         <v>1.5031000000000001</v>
       </c>
-      <c r="U11">
+      <c r="W11">
         <v>8.3856256482771094</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X11">
+        <v>59.122840326561501</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C12">
         <v>2021</v>
@@ -1158,48 +1257,54 @@
         <v>6.7497766470398597</v>
       </c>
       <c r="J12">
+        <v>50.7541757175008</v>
+      </c>
+      <c r="K12">
         <v>30.9853470588235</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>0.50819839572192504</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>0.71835454545454502</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>1.4267192513369</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>1.5031000000000001</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>5.5865517909580102</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
+        <v>48.426450386926902</v>
+      </c>
+      <c r="R12">
         <v>26.3721113636364</v>
       </c>
-      <c r="Q12">
+      <c r="S12">
         <v>3.6210344827586199E-2</v>
       </c>
-      <c r="R12">
+      <c r="T12">
         <v>0.21684827586206901</v>
       </c>
-      <c r="S12">
+      <c r="U12">
         <v>0.69469310344827595</v>
       </c>
-      <c r="T12">
+      <c r="V12">
         <v>1.5031000000000001</v>
       </c>
-      <c r="U12">
+      <c r="W12">
         <v>10.207449943064301</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C13">
         <v>2023</v>
@@ -1223,45 +1328,51 @@
         <v>15.1318753281131</v>
       </c>
       <c r="J13">
+        <v>50.035098598446702</v>
+      </c>
+      <c r="K13">
         <v>32.5036594202899</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>0.50214766355140195</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>0.71881869158878497</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>1.4487869158878499</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>1.4835915887850499</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>14.9101534936639</v>
       </c>
-      <c r="P13">
+      <c r="R13">
         <v>26.837142647058801</v>
       </c>
-      <c r="Q13">
+      <c r="S13">
         <v>0.16229727272727301</v>
       </c>
-      <c r="S13">
+      <c r="U13">
         <v>0.66718636363636397</v>
       </c>
-      <c r="T13">
+      <c r="V13">
         <v>1.4841236363636401</v>
       </c>
-      <c r="U13">
+      <c r="W13">
         <v>15.930087239926401</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X13">
+        <v>55.428971023149401</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C14">
         <v>2017</v>
@@ -1285,24 +1396,33 @@
         <v>9.6881432665145102</v>
       </c>
       <c r="J14">
+        <v>46.990116801437502</v>
+      </c>
+      <c r="K14">
         <v>29.748872533333401</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>9.8945198949871198</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
+        <v>44.561403508771903</v>
+      </c>
+      <c r="R14">
         <v>26.876158823529298</v>
       </c>
-      <c r="U14">
+      <c r="W14">
         <v>8.1518960369946303</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X14">
+        <v>55.038759689922401</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C15">
         <v>2019</v>
@@ -1326,48 +1446,57 @@
         <v>17.103301700844</v>
       </c>
       <c r="J15">
+        <v>59.161566864020998</v>
+      </c>
+      <c r="K15">
         <v>30.460596428571399</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>0.43789917695473202</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>0.67167448559670795</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>1.6036736625514401</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>1.47446625514403</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>18.951313289501002</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
+        <v>59.112028910686597</v>
+      </c>
+      <c r="R15">
         <v>25.7891012048193</v>
       </c>
-      <c r="Q15">
+      <c r="S15">
         <v>0</v>
       </c>
-      <c r="R15">
+      <c r="T15">
         <v>0.113695652173913</v>
       </c>
-      <c r="S15">
+      <c r="U15">
         <v>8.7481521739130402E-2</v>
       </c>
-      <c r="T15">
+      <c r="V15">
         <v>1.5031000000000001</v>
       </c>
-      <c r="U15">
+      <c r="W15">
         <v>3.2487321949654899</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X15">
+        <v>59.515190121799698</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C16">
         <v>2021</v>
@@ -1391,45 +1520,51 @@
         <v>10.8131654651469</v>
       </c>
       <c r="J16">
+        <v>53.474629837217499</v>
+      </c>
+      <c r="K16">
         <v>30.106375624999998</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>0.24966682464455001</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>0.41984265402843601</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>1.44993601895735</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>1.4767663507108999</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>10.947640305687401</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
+        <v>50.863372884743697</v>
+      </c>
+      <c r="R16">
         <v>27.304628571428601</v>
       </c>
-      <c r="Q16">
+      <c r="S16">
         <v>9.5463636363636403E-2</v>
       </c>
-      <c r="S16">
+      <c r="U16">
         <v>0</v>
       </c>
-      <c r="T16">
+      <c r="V16">
         <v>1.5031000000000001</v>
       </c>
-      <c r="U16">
+      <c r="W16">
         <v>9.7540411074969704</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C17">
         <v>2023</v>
@@ -1453,42 +1588,48 @@
         <v>9.6558551926316305</v>
       </c>
       <c r="J17">
+        <v>52.277966503007399</v>
+      </c>
+      <c r="K17">
         <v>30.2846075268817</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>0.43886515151515099</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>0.66031969696969695</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>1.48304621212121</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>1.48728636363636</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>10.253570175401601</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
+        <v>49.6712112701628</v>
+      </c>
+      <c r="R17">
         <v>26.754984482758601</v>
       </c>
-      <c r="Q17">
+      <c r="S17">
         <v>2.9169444444444401E-2</v>
       </c>
-      <c r="T17">
+      <c r="V17">
         <v>1.4934361111111101</v>
       </c>
-      <c r="U17">
+      <c r="W17">
         <v>5.84778645295824</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C18">
         <v>2017</v>
@@ -1512,24 +1653,33 @@
         <v>1.0232002879920601</v>
       </c>
       <c r="J18">
+        <v>35.9375</v>
+      </c>
+      <c r="K18">
         <v>24.594141666666602</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>4.7941925133241803</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
+        <v>34.078212290502698</v>
+      </c>
+      <c r="R18">
         <v>21.908490425531902</v>
       </c>
-      <c r="U18">
+      <c r="W18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X18">
+        <v>38.297872340425499</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C19">
         <v>2019</v>
@@ -1553,48 +1703,57 @@
         <v>5.3103268230977898</v>
       </c>
       <c r="J19">
+        <v>53.577143909081798</v>
+      </c>
+      <c r="K19">
         <v>27.872644680851099</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>0</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>4.6696428571428601E-3</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>1.6583035714285699E-2</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>1.5031000000000001</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>6.6264077539080102</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
+        <v>53.932584269662897</v>
+      </c>
+      <c r="R19">
         <v>23.583446296296302</v>
       </c>
-      <c r="Q19">
+      <c r="S19">
         <v>0</v>
       </c>
-      <c r="R19">
+      <c r="T19">
         <v>0</v>
       </c>
-      <c r="S19">
+      <c r="U19">
         <v>4.7992248062015503E-3</v>
       </c>
-      <c r="T19">
+      <c r="V19">
         <v>1.4114054263565901</v>
       </c>
-      <c r="U19">
+      <c r="W19">
         <v>4.9700168637945703</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X19">
+        <v>53.489116517285602</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C20">
         <v>2021</v>
@@ -1614,46 +1773,46 @@
       <c r="I20">
         <v>10.134323020186599</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>27.424741666666701</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>1.03970297029703E-2</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
       </c>
       <c r="M20">
         <v>0</v>
       </c>
       <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
         <v>1.5031000000000001</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>10.9288667602031</v>
       </c>
-      <c r="P20">
+      <c r="R20">
         <v>26.101400000000002</v>
       </c>
-      <c r="Q20">
+      <c r="S20">
         <v>1.9446296296296298E-2</v>
       </c>
-      <c r="R20">
+      <c r="T20">
         <v>0</v>
       </c>
-      <c r="T20">
+      <c r="V20">
         <v>1.4708870370370399</v>
       </c>
-      <c r="U20">
+      <c r="W20">
         <v>9.4234614530104395</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C21">
         <v>2023</v>
@@ -1671,39 +1830,42 @@
         <v>9.1895490599072591</v>
       </c>
       <c r="J21">
+        <v>91.532722751258603</v>
+      </c>
+      <c r="K21">
         <v>27.4968315789474</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>3.9378749999999997E-2</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>0</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>1.4857050000000001</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>10.245514569745501</v>
       </c>
-      <c r="P21">
+      <c r="R21">
         <v>25.454870588235298</v>
       </c>
-      <c r="Q21">
+      <c r="S21">
         <v>4.2628205128205102E-2</v>
       </c>
-      <c r="T21">
+      <c r="V21">
         <v>1.44078461538462</v>
       </c>
-      <c r="U21">
+      <c r="W21">
         <v>8.1667907023980195</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C22">
         <v>2017</v>
@@ -1727,24 +1889,33 @@
         <v>3.0856035216988098</v>
       </c>
       <c r="J22">
+        <v>50.946142649199402</v>
+      </c>
+      <c r="K22">
         <v>30.280024015748101</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>3.5369308409673001</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
+        <v>51.077586206896498</v>
+      </c>
+      <c r="R22">
         <v>24.6705906779661</v>
       </c>
-      <c r="U22">
+      <c r="W22">
         <v>2.6008293691199</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X22">
+        <v>50.672645739910301</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C23">
         <v>2019</v>
@@ -1768,48 +1939,57 @@
         <v>4.6224231508303202</v>
       </c>
       <c r="J23">
+        <v>55.945588445602702</v>
+      </c>
+      <c r="K23">
         <v>29.21275</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>0.26252500000000001</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>0.45582121212121202</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>1.30245757575758</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>1.5031000000000001</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>7.20846317552129</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
+        <v>56.090669516314499</v>
+      </c>
+      <c r="R23">
         <v>25.714738759689901</v>
       </c>
-      <c r="Q23">
+      <c r="S23">
         <v>0</v>
       </c>
-      <c r="R23">
+      <c r="T23">
         <v>8.9828244274809205E-2</v>
       </c>
-      <c r="S23">
+      <c r="U23">
         <v>0.446922900763359</v>
       </c>
-      <c r="T23">
+      <c r="V23">
         <v>1.5031000000000001</v>
       </c>
-      <c r="U23">
+      <c r="W23">
         <v>2.2956058764469001</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X23">
+        <v>55.801424594135398</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C24">
         <v>2021</v>
@@ -1833,48 +2013,57 @@
         <v>8.6689353740948007</v>
       </c>
       <c r="J24">
+        <v>69.070818219159904</v>
+      </c>
+      <c r="K24">
         <v>30.971080519480498</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>0.253351428571429</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>0.44590000000000002</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>1.53972476190476</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>1.5031000000000001</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>6.7270180624538103</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
+        <v>54.748131761119502</v>
+      </c>
+      <c r="R24">
         <v>26.849068750000001</v>
       </c>
-      <c r="Q24">
+      <c r="S24">
         <v>3.2815625000000001E-2</v>
       </c>
-      <c r="R24">
+      <c r="T24">
         <v>0.13921718750000001</v>
       </c>
-      <c r="S24">
+      <c r="U24">
         <v>0.36047578125000002</v>
       </c>
-      <c r="T24">
+      <c r="V24">
         <v>1.5031000000000001</v>
       </c>
-      <c r="U24">
+      <c r="W24">
         <v>10.385678907306399</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X24">
+        <v>80.199400031663899</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C25">
         <v>2023</v>
@@ -1897,46 +2086,49 @@
       <c r="I25">
         <v>4.5750855823013596</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>26.7433301204819</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>6.5631250000000002E-2</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>0.84898035714285702</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>1.4783392857142901</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>6.8923339083120903</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
+        <v>52.500093636465799</v>
+      </c>
+      <c r="R25">
         <v>28.667035087719299</v>
       </c>
-      <c r="Q25">
+      <c r="S25">
         <v>1.23541176470588E-2</v>
       </c>
-      <c r="R25">
+      <c r="T25">
         <v>0.178583529411765</v>
       </c>
-      <c r="S25">
+      <c r="U25">
         <v>0.33292588235294102</v>
       </c>
-      <c r="T25">
+      <c r="V25">
         <v>1.4949141176470599</v>
       </c>
-      <c r="U25">
+      <c r="W25">
         <v>2.7900886540493</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C26">
         <v>2017</v>
@@ -1960,24 +2152,33 @@
         <v>5.4914142625512001</v>
       </c>
       <c r="J26">
+        <v>55.150753768844197</v>
+      </c>
+      <c r="K26">
         <v>30.7100433121017</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>11.874766728217899</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
+        <v>49.723756906077298</v>
+      </c>
+      <c r="R26">
         <v>24.1724643835616</v>
       </c>
-      <c r="U26">
+      <c r="W26">
         <v>3.0662451547568299</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X26">
+        <v>66.798418972332001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C27">
         <v>2019</v>
@@ -2001,48 +2202,57 @@
         <v>8.4927922785142709</v>
       </c>
       <c r="J27">
+        <v>59.178829878579201</v>
+      </c>
+      <c r="K27">
         <v>29.456263120567399</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>0.13218041958042001</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>0.34528811188811198</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>1.5868839160839201</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>1.4885027972028</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>10.0808379529227</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
+        <v>59.883546333917202</v>
+      </c>
+      <c r="R27">
         <v>25.961511214953301</v>
       </c>
-      <c r="Q27">
+      <c r="S27">
         <v>9.4603603603603606E-3</v>
       </c>
-      <c r="R27">
+      <c r="T27">
         <v>0.132041441441441</v>
       </c>
-      <c r="S27">
+      <c r="U27">
         <v>0.273886486486486</v>
       </c>
-      <c r="T27">
+      <c r="V27">
         <v>1.4968315315315299</v>
       </c>
-      <c r="U27">
+      <c r="W27">
         <v>7.9248025340486903</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X27">
+        <v>58.947979956912199</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C28">
         <v>2021</v>
@@ -2066,42 +2276,51 @@
         <v>14.9195393833545</v>
       </c>
       <c r="J28">
+        <v>68.987437960055303</v>
+      </c>
+      <c r="K28">
         <v>28.873173469387801</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>0.18847948717948701</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>1.30016282051282</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>1.4675461538461501</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>18.925117160235299</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
+        <v>52.297376313257999</v>
+      </c>
+      <c r="R28">
         <v>26.183321367521401</v>
       </c>
-      <c r="Q28">
+      <c r="S28">
         <v>3.6070909090909098E-2</v>
       </c>
-      <c r="S28">
+      <c r="U28">
         <v>0.29428181818181798</v>
       </c>
-      <c r="T28">
+      <c r="V28">
         <v>1.4904490909090899</v>
       </c>
-      <c r="U28">
+      <c r="W28">
         <v>12.7041252969327</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X28">
+        <v>76.837800057334604</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>2023</v>
@@ -2125,45 +2344,51 @@
         <v>15.853858464109599</v>
       </c>
       <c r="J29">
+        <v>64.192320769777595</v>
+      </c>
+      <c r="K29">
         <v>27.5950177419355</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>3.3513829787234002E-2</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>0.22156276595744701</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>1.2421287234042599</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>1.42188936170213</v>
       </c>
-      <c r="O29">
+      <c r="P29">
         <v>18.070608945356302</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
+        <v>50.626988583192997</v>
+      </c>
+      <c r="R29">
         <v>26.048611320754699</v>
       </c>
-      <c r="Q29">
+      <c r="S29">
         <v>4.3754166666666698E-2</v>
       </c>
-      <c r="S29">
+      <c r="U29">
         <v>0.66609305555555598</v>
       </c>
-      <c r="T29">
+      <c r="V29">
         <v>1.4451166666666699</v>
       </c>
-      <c r="U29">
+      <c r="W29">
         <v>14.4243661126115</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C30">
         <v>2017</v>
@@ -2187,24 +2412,33 @@
         <v>1.4297177004906501</v>
       </c>
       <c r="J30">
+        <v>60.561299852289501</v>
+      </c>
+      <c r="K30">
         <v>28.097167527675399</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>3.8380435493333498</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
+        <v>57.665903890160102</v>
+      </c>
+      <c r="R30">
         <v>23.628895035460999</v>
       </c>
-      <c r="U30">
+      <c r="W30">
         <v>0.21910309573260001</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X30">
+        <v>65.8333333333333</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>2019</v>
@@ -2228,48 +2462,57 @@
         <v>7.7735977490855603</v>
       </c>
       <c r="J31">
+        <v>72.055555684075003</v>
+      </c>
+      <c r="K31">
         <v>26.852681502890199</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>4.7195505617977501E-2</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>0.16657471910112401</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>1.3317803370786501</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>1.46015730337079</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>15.0639797838598</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
+        <v>72.301406488298099</v>
+      </c>
+      <c r="R31">
         <v>24.1178448</v>
       </c>
-      <c r="Q31">
+      <c r="S31">
         <v>0</v>
       </c>
-      <c r="R31">
+      <c r="T31">
         <v>6.6350746268656696E-2</v>
       </c>
-      <c r="S31">
+      <c r="U31">
         <v>0.201220895522388</v>
       </c>
-      <c r="T31">
+      <c r="V31">
         <v>1.4719447761194</v>
       </c>
-      <c r="U31">
+      <c r="W31">
         <v>3.58133168174533</v>
       </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X31">
+        <v>71.939631078814998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C32">
         <v>2021</v>
@@ -2293,42 +2536,51 @@
         <v>6.2479229401273999</v>
       </c>
       <c r="J32">
+        <v>71.129153926698194</v>
+      </c>
+      <c r="K32">
         <v>28.540724324324302</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>6.7027659574468101E-2</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>1.29062340425532</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>1.4586872340425501</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>8.2908761544309098</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
+        <v>60.282253391739303</v>
+      </c>
+      <c r="R32">
         <v>23.941962499999999</v>
       </c>
-      <c r="Q32">
+      <c r="S32">
         <v>2.85741496598639E-2</v>
       </c>
-      <c r="S32">
+      <c r="U32">
         <v>0.298137414965986</v>
       </c>
-      <c r="T32">
+      <c r="V32">
         <v>1.49836666666667</v>
       </c>
-      <c r="U32">
+      <c r="W32">
         <v>4.9301079419663196</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X32">
+        <v>77.824889803382405</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C33">
         <v>2023</v>
@@ -2349,42 +2601,51 @@
         <v>5.3215650052040697</v>
       </c>
       <c r="J33">
+        <v>64.867967853042501</v>
+      </c>
+      <c r="K33">
         <v>26.859821505376299</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>0.117826732673267</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>1.06475940594059</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>1.4617653465346501</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>8.9916236825386697</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
+        <v>56.953260242354297</v>
+      </c>
+      <c r="R33">
         <v>26.145995604395601</v>
       </c>
-      <c r="Q33">
+      <c r="S33">
         <v>0.101322105263158</v>
       </c>
-      <c r="S33">
+      <c r="U33">
         <v>0.44270842105263197</v>
       </c>
-      <c r="T33">
+      <c r="V33">
         <v>1.5031000000000001</v>
       </c>
-      <c r="U33">
+      <c r="W33">
         <v>2.7474165731537901</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X33">
+        <v>70.099160945842897</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C34">
         <v>2017</v>
@@ -2408,24 +2669,33 @@
         <v>3.6932612694310198</v>
       </c>
       <c r="J34">
+        <v>53.945666235446303</v>
+      </c>
+      <c r="K34">
         <v>29.1732840390879</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>6.9426044321662896</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
+        <v>58.777120315581797</v>
+      </c>
+      <c r="R34">
         <v>22.6522397260273</v>
       </c>
-      <c r="U34">
+      <c r="W34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X34">
+        <v>44.736842105263101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C35">
         <v>2019</v>
@@ -2449,48 +2719,57 @@
         <v>3.7181801786781699</v>
       </c>
       <c r="J35">
+        <v>65.708544692424994</v>
+      </c>
+      <c r="K35">
         <v>30.0693297709924</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>4.4370422535211299E-2</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>0.20862746478873201</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>1.49867816901408</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>1.4835</v>
       </c>
-      <c r="O35">
+      <c r="P35">
         <v>7.09567495722417</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
+        <v>67.141979627567395</v>
+      </c>
+      <c r="R35">
         <v>27.486713725490201</v>
       </c>
-      <c r="Q35">
+      <c r="S35">
         <v>0</v>
       </c>
-      <c r="R35">
+      <c r="T35">
         <v>4.5086206896551698E-2</v>
       </c>
-      <c r="S35">
+      <c r="U35">
         <v>0.31369396551724099</v>
       </c>
-      <c r="T35">
+      <c r="V35">
         <v>1.5031000000000001</v>
       </c>
-      <c r="U35">
+      <c r="W35">
         <v>0.59438606255578297</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X35">
+        <v>64.5190374837413</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C36">
         <v>2021</v>
@@ -2514,42 +2793,51 @@
         <v>3.19013117571015</v>
       </c>
       <c r="J36">
+        <v>60.731185548610704</v>
+      </c>
+      <c r="K36">
         <v>26.866946590909102</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>4.5656521739130401E-2</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>0.20054260869565199</v>
       </c>
-      <c r="M36">
+      <c r="N36">
         <v>1.3770765217391301</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>1.4909991304347801</v>
       </c>
-      <c r="O36">
+      <c r="P36">
         <v>3.6009388635042598</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
+        <v>52.3194850152341</v>
+      </c>
+      <c r="R36">
         <v>24.825323728813601</v>
       </c>
-      <c r="Q36">
+      <c r="S36">
         <v>0</v>
       </c>
-      <c r="T36">
+      <c r="V36">
         <v>1.48691860465116</v>
       </c>
-      <c r="U36">
+      <c r="W36">
         <v>2.8032299251420998</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X36">
+        <v>68.188053859707296</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C37">
         <v>2023</v>
@@ -2573,42 +2861,48 @@
         <v>4.4139041756786499</v>
       </c>
       <c r="J37">
+        <v>56.8011516387973</v>
+      </c>
+      <c r="K37">
         <v>26.8033303797468</v>
       </c>
-      <c r="K37">
+      <c r="L37">
         <v>3.9583333333333297E-2</v>
       </c>
-      <c r="M37">
+      <c r="N37">
         <v>1.3727714285714301</v>
       </c>
-      <c r="N37">
+      <c r="O37">
         <v>1.49481666666667</v>
       </c>
-      <c r="O37">
+      <c r="P37">
         <v>6.7297029016718897</v>
       </c>
-      <c r="P37">
+      <c r="Q37">
+        <v>53.247665896998299</v>
+      </c>
+      <c r="R37">
         <v>24.863262121212099</v>
       </c>
-      <c r="Q37">
+      <c r="S37">
         <v>0</v>
       </c>
-      <c r="R37">
+      <c r="T37">
         <v>0.12154225352112701</v>
       </c>
-      <c r="T37">
+      <c r="V37">
         <v>1.4639</v>
       </c>
-      <c r="U37">
+      <c r="W37">
         <v>2.6338023729173301</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C38">
         <v>2017</v>
@@ -2632,24 +2926,33 @@
         <v>18.260303562294499</v>
       </c>
       <c r="J38">
+        <v>48.427073403241103</v>
+      </c>
+      <c r="K38">
         <v>28.832202133333201</v>
       </c>
-      <c r="O38">
+      <c r="P38">
         <v>35.0091337742072</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
+        <v>53.794940079893401</v>
+      </c>
+      <c r="R38">
         <v>26.168406081080999</v>
       </c>
-      <c r="U38">
+      <c r="W38">
         <v>3.12884174935169</v>
       </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X38">
+        <v>34.899328859060397</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C39">
         <v>2019</v>
@@ -2673,48 +2976,57 @@
         <v>18.974803156396501</v>
       </c>
       <c r="J39">
+        <v>60.606714564575299</v>
+      </c>
+      <c r="K39">
         <v>27.9451671755725</v>
       </c>
-      <c r="K39">
+      <c r="L39">
         <v>0.33050000000000002</v>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>0.48827122302158299</v>
       </c>
-      <c r="M39">
+      <c r="N39">
         <v>1.1997309352518</v>
       </c>
-      <c r="N39">
+      <c r="O39">
         <v>1.4731014388489201</v>
       </c>
-      <c r="O39">
+      <c r="P39">
         <v>24.0126859342644</v>
       </c>
-      <c r="P39">
+      <c r="Q39">
+        <v>60.219715498695301</v>
+      </c>
+      <c r="R39">
         <v>26.051105633802798</v>
       </c>
-      <c r="Q39">
+      <c r="S39">
         <v>7.5497385620915E-2</v>
       </c>
-      <c r="R39">
+      <c r="T39">
         <v>0.227365359477124</v>
       </c>
-      <c r="S39">
+      <c r="U39">
         <v>0.743224836601307</v>
       </c>
-      <c r="T39">
+      <c r="V39">
         <v>1.4849091503267999</v>
       </c>
-      <c r="U39">
+      <c r="W39">
         <v>15.755758312932301</v>
       </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X39">
+        <v>60.865713039162301</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>2021</v>
@@ -2738,48 +3050,57 @@
         <v>9.5082586308842991</v>
       </c>
       <c r="J40">
+        <v>62.069957839003798</v>
+      </c>
+      <c r="K40">
         <v>28.029784848484901</v>
       </c>
-      <c r="K40">
+      <c r="L40">
         <v>0.27938899082568802</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>0.40543027522935798</v>
       </c>
-      <c r="M40">
+      <c r="N40">
         <v>1.0434614678899099</v>
       </c>
-      <c r="N40">
+      <c r="O40">
         <v>1.4903330275229401</v>
       </c>
-      <c r="O40">
+      <c r="P40">
         <v>7.1343552593198902</v>
       </c>
-      <c r="P40">
+      <c r="Q40">
+        <v>56.171338906705998</v>
+      </c>
+      <c r="R40">
         <v>26.573770588235298</v>
       </c>
-      <c r="Q40">
+      <c r="S40">
         <v>3.7773381294963999E-2</v>
       </c>
-      <c r="R40">
+      <c r="T40">
         <v>0.198838129496403</v>
       </c>
-      <c r="S40">
+      <c r="U40">
         <v>0.63026043165467605</v>
       </c>
-      <c r="T40">
+      <c r="V40">
         <v>1.4830769784172699</v>
       </c>
-      <c r="U40">
+      <c r="W40">
         <v>11.8415298442</v>
       </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X40">
+        <v>66.603804831777396</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C41">
         <v>2023</v>
@@ -2803,45 +3124,54 @@
         <v>19.8643719691351</v>
       </c>
       <c r="J41">
+        <v>59.5897187047741</v>
+      </c>
+      <c r="K41">
         <v>28.194708870967698</v>
       </c>
-      <c r="K41">
+      <c r="L41">
         <v>0.24076031746031701</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>0.374820105820106</v>
       </c>
-      <c r="M41">
+      <c r="N41">
         <v>1.0715894179894201</v>
       </c>
-      <c r="N41">
+      <c r="O41">
         <v>1.38929153439153</v>
       </c>
-      <c r="O41">
+      <c r="P41">
         <v>26.300115223932099</v>
       </c>
-      <c r="P41">
+      <c r="Q41">
+        <v>55.571715247091198</v>
+      </c>
+      <c r="R41">
         <v>25.2214457142857</v>
       </c>
-      <c r="Q41">
+      <c r="S41">
         <v>5.2071074380165297E-2</v>
       </c>
-      <c r="S41">
+      <c r="U41">
         <v>0.32580413223140497</v>
       </c>
-      <c r="T41">
+      <c r="V41">
         <v>1.46284710743802</v>
       </c>
-      <c r="U41">
+      <c r="W41">
         <v>12.334778174131699</v>
       </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X41">
+        <v>62.871484343877</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2017</v>
@@ -2865,24 +3195,33 @@
         <v>3.3715385826447699</v>
       </c>
       <c r="J42">
+        <v>44.505494505494497</v>
+      </c>
+      <c r="K42">
         <v>25.169612121212101</v>
       </c>
-      <c r="O42">
+      <c r="P42">
         <v>4.1415127005947898</v>
       </c>
-      <c r="P42">
+      <c r="Q42">
+        <v>46.747967479674799</v>
+      </c>
+      <c r="R42">
         <v>24.649011764705801</v>
       </c>
-      <c r="U42">
+      <c r="W42">
         <v>2.8634680461448001</v>
       </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X42">
+        <v>39.830508474576199</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C43">
         <v>2019</v>
@@ -2906,48 +3245,57 @@
         <v>8.7842637621195507</v>
       </c>
       <c r="J43">
+        <v>53.266028478518201</v>
+      </c>
+      <c r="K43">
         <v>25.108284615384601</v>
       </c>
-      <c r="K43">
+      <c r="L43">
         <v>2.56121951219512E-2</v>
       </c>
-      <c r="L43">
+      <c r="M43">
         <v>3.1890243902439001E-3</v>
       </c>
-      <c r="M43">
+      <c r="N43">
         <v>1.5100000000000001E-2</v>
       </c>
-      <c r="N43">
+      <c r="O43">
         <v>1.2741170731707301</v>
       </c>
-      <c r="O43">
+      <c r="P43">
         <v>13.294395119161299</v>
       </c>
-      <c r="P43">
+      <c r="Q43">
+        <v>54.6802786783473</v>
+      </c>
+      <c r="R43">
         <v>24.5994909090909</v>
-      </c>
-      <c r="Q43">
-        <v>0</v>
-      </c>
-      <c r="R43">
-        <v>0</v>
       </c>
       <c r="S43">
         <v>0</v>
       </c>
       <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
         <v>1.3714621621621601</v>
       </c>
-      <c r="U43">
+      <c r="W43">
         <v>5.8021943191146299</v>
       </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X43">
+        <v>52.428082005546798</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C44">
         <v>2021</v>
@@ -2968,42 +3316,45 @@
         <v>8.2652421702484098</v>
       </c>
       <c r="J44">
+        <v>84.105872348285203</v>
+      </c>
+      <c r="K44">
         <v>27.7234941176471</v>
       </c>
-      <c r="K44">
+      <c r="L44">
         <v>5.3278260869565199E-2</v>
       </c>
-      <c r="M44">
+      <c r="N44">
         <v>0.294586956521739</v>
       </c>
-      <c r="N44">
+      <c r="O44">
         <v>1.47284782608696</v>
       </c>
-      <c r="O44">
+      <c r="P44">
         <v>6.3221439555200396</v>
       </c>
-      <c r="P44">
+      <c r="R44">
         <v>24.762770588235298</v>
       </c>
-      <c r="Q44">
+      <c r="S44">
         <v>1.54426470588235E-2</v>
       </c>
-      <c r="R44">
+      <c r="T44">
         <v>0</v>
       </c>
-      <c r="T44">
+      <c r="V44">
         <v>1.2728720588235301</v>
       </c>
-      <c r="U44">
+      <c r="W44">
         <v>9.7681955820560606</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C45">
         <v>2023</v>
@@ -3021,27 +3372,30 @@
         <v>11.9389222251462</v>
       </c>
       <c r="J45">
+        <v>79.190671201499299</v>
+      </c>
+      <c r="K45">
         <v>28.416886666666699</v>
       </c>
-      <c r="K45">
+      <c r="L45">
         <v>7.9782352941176499E-2</v>
       </c>
-      <c r="N45">
+      <c r="O45">
         <v>1.08504411764706</v>
       </c>
-      <c r="O45">
+      <c r="P45">
         <v>12.0317802319202</v>
       </c>
-      <c r="P45">
+      <c r="R45">
         <v>25.739673076923101</v>
       </c>
-      <c r="Q45">
+      <c r="S45">
         <v>4.3754166666666698E-2</v>
       </c>
-      <c r="T45">
+      <c r="V45">
         <v>1.42337291666667</v>
       </c>
-      <c r="U45">
+      <c r="W45">
         <v>11.8766557296205</v>
       </c>
     </row>
